--- a/2773 Monitoring.xlsx
+++ b/2773 Monitoring.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0" codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\gitrepos\decarb_monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB963D78-A192-4356-A973-981289A30EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EAF3BD-C833-443A-A03B-CD9EA6231245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1845" windowWidth="29040" windowHeight="17520" tabRatio="775" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,14 +35,14 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Reto Dettli - Persönliche Ansicht" guid="{EFCCBDBE-703D-49A8-BFD5-C70DFC4C6246}" mergeInterval="0" personalView="1" maximized="1" xWindow="182" yWindow="-1449" windowWidth="2578" windowHeight="1398" activeSheetId="1"/>
+    <customWorkbookView name="w10 Test - Persönliche Ansicht" guid="{F0C3F358-38F8-4A2B-A44F-0486E20EA4EB}" mergeInterval="0" personalView="1" xWindow="153" yWindow="43" windowWidth="1713" windowHeight="1088" activeSheetId="1"/>
+    <customWorkbookView name="Daniel Moos - Persönliche Ansicht" guid="{9D53A792-EE49-4CB1-A328-80A3B1745755}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="-8" windowWidth="1936" windowHeight="1216" activeSheetId="1" showComments="commNone"/>
+    <customWorkbookView name="Ernst Haas - Persönliche Ansicht" guid="{E9B280C6-F6C1-4D6E-A20C-7C4266B3269C}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="923" activeSheetId="1"/>
+    <customWorkbookView name="Urs Müller - Persönliche Ansicht" guid="{684E191D-B776-4614-A9A6-09F48EE40BD1}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="978" activeSheetId="1"/>
+    <customWorkbookView name="Dmoos - Persönliche Ansicht" guid="{D178FE1B-3B10-414B-86B8-943130264B26}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1176" activeSheetId="1"/>
+    <customWorkbookView name="Andrea Binkert - Persönliche Ansicht" guid="{2A6B7D3A-520D-4798-8230-1DC17916761C}" mergeInterval="0" personalView="1" xWindow="492" windowWidth="948" windowHeight="860" activeSheetId="1"/>
     <customWorkbookView name="Basil Odermatt - Persönliche Ansicht" guid="{59C26AB4-86C6-4447-8F9F-F1FCBFE3A683}" mergeInterval="0" personalView="1" maximized="1" xWindow="2552" yWindow="-6" windowWidth="2576" windowHeight="1426" activeSheetId="1"/>
-    <customWorkbookView name="Andrea Binkert - Persönliche Ansicht" guid="{2A6B7D3A-520D-4798-8230-1DC17916761C}" mergeInterval="0" personalView="1" xWindow="492" windowWidth="948" windowHeight="860" activeSheetId="1"/>
-    <customWorkbookView name="Dmoos - Persönliche Ansicht" guid="{D178FE1B-3B10-414B-86B8-943130264B26}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1176" activeSheetId="1"/>
-    <customWorkbookView name="Urs Müller - Persönliche Ansicht" guid="{684E191D-B776-4614-A9A6-09F48EE40BD1}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="978" activeSheetId="1"/>
-    <customWorkbookView name="Ernst Haas - Persönliche Ansicht" guid="{E9B280C6-F6C1-4D6E-A20C-7C4266B3269C}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="923" activeSheetId="1"/>
-    <customWorkbookView name="Daniel Moos - Persönliche Ansicht" guid="{9D53A792-EE49-4CB1-A328-80A3B1745755}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="-8" windowWidth="1936" windowHeight="1216" activeSheetId="1" showComments="commNone"/>
-    <customWorkbookView name="w10 Test - Persönliche Ansicht" guid="{F0C3F358-38F8-4A2B-A44F-0486E20EA4EB}" mergeInterval="0" personalView="1" xWindow="153" yWindow="43" windowWidth="1713" windowHeight="1088" activeSheetId="1"/>
-    <customWorkbookView name="Reto Dettli - Persönliche Ansicht" guid="{EFCCBDBE-703D-49A8-BFD5-C70DFC4C6246}" mergeInterval="0" personalView="1" maximized="1" xWindow="182" yWindow="-1449" windowWidth="2578" windowHeight="1398" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5675,7 +5675,7 @@
     </row>
     <row r="10" spans="1:31" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>380</v>
@@ -7765,15 +7765,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c16c412-41a7-483e-8458-9b4c6e041c8c">
@@ -7782,6 +7773,15 @@
     <TaxCatchAll xmlns="9ff67bf8-4dc4-49ec-8a2f-3c58a02da8ea" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7990,14 +7990,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E4C368-1DF5-422B-BD39-8846CE2351EE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A314DA-0F62-4E10-94F7-DBFCC9F3B707}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -8010,6 +8002,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E4C368-1DF5-422B-BD39-8846CE2351EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/2773 Monitoring.xlsx
+++ b/2773 Monitoring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\gitrepos\decarb_monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EAF3BD-C833-443A-A03B-CD9EA6231245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF6B899-68AB-4B2C-A431-EEDDFB2F6C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1845" windowWidth="29040" windowHeight="17520" tabRatio="775" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="3165" windowWidth="29040" windowHeight="17520" tabRatio="775" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kostenübersicht" sheetId="51" state="hidden" r:id="rId1"/>
@@ -35,14 +35,14 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Basil Odermatt - Persönliche Ansicht" guid="{59C26AB4-86C6-4447-8F9F-F1FCBFE3A683}" mergeInterval="0" personalView="1" maximized="1" xWindow="2552" yWindow="-6" windowWidth="2576" windowHeight="1426" activeSheetId="1"/>
+    <customWorkbookView name="Andrea Binkert - Persönliche Ansicht" guid="{2A6B7D3A-520D-4798-8230-1DC17916761C}" mergeInterval="0" personalView="1" xWindow="492" windowWidth="948" windowHeight="860" activeSheetId="1"/>
+    <customWorkbookView name="Dmoos - Persönliche Ansicht" guid="{D178FE1B-3B10-414B-86B8-943130264B26}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1176" activeSheetId="1"/>
+    <customWorkbookView name="Urs Müller - Persönliche Ansicht" guid="{684E191D-B776-4614-A9A6-09F48EE40BD1}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="978" activeSheetId="1"/>
+    <customWorkbookView name="Ernst Haas - Persönliche Ansicht" guid="{E9B280C6-F6C1-4D6E-A20C-7C4266B3269C}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="923" activeSheetId="1"/>
+    <customWorkbookView name="Daniel Moos - Persönliche Ansicht" guid="{9D53A792-EE49-4CB1-A328-80A3B1745755}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="-8" windowWidth="1936" windowHeight="1216" activeSheetId="1" showComments="commNone"/>
+    <customWorkbookView name="w10 Test - Persönliche Ansicht" guid="{F0C3F358-38F8-4A2B-A44F-0486E20EA4EB}" mergeInterval="0" personalView="1" xWindow="153" yWindow="43" windowWidth="1713" windowHeight="1088" activeSheetId="1"/>
     <customWorkbookView name="Reto Dettli - Persönliche Ansicht" guid="{EFCCBDBE-703D-49A8-BFD5-C70DFC4C6246}" mergeInterval="0" personalView="1" maximized="1" xWindow="182" yWindow="-1449" windowWidth="2578" windowHeight="1398" activeSheetId="1"/>
-    <customWorkbookView name="w10 Test - Persönliche Ansicht" guid="{F0C3F358-38F8-4A2B-A44F-0486E20EA4EB}" mergeInterval="0" personalView="1" xWindow="153" yWindow="43" windowWidth="1713" windowHeight="1088" activeSheetId="1"/>
-    <customWorkbookView name="Daniel Moos - Persönliche Ansicht" guid="{9D53A792-EE49-4CB1-A328-80A3B1745755}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="-8" windowWidth="1936" windowHeight="1216" activeSheetId="1" showComments="commNone"/>
-    <customWorkbookView name="Ernst Haas - Persönliche Ansicht" guid="{E9B280C6-F6C1-4D6E-A20C-7C4266B3269C}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="923" activeSheetId="1"/>
-    <customWorkbookView name="Urs Müller - Persönliche Ansicht" guid="{684E191D-B776-4614-A9A6-09F48EE40BD1}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1916" windowHeight="978" activeSheetId="1"/>
-    <customWorkbookView name="Dmoos - Persönliche Ansicht" guid="{D178FE1B-3B10-414B-86B8-943130264B26}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1176" activeSheetId="1"/>
-    <customWorkbookView name="Andrea Binkert - Persönliche Ansicht" guid="{2A6B7D3A-520D-4798-8230-1DC17916761C}" mergeInterval="0" personalView="1" xWindow="492" windowWidth="948" windowHeight="860" activeSheetId="1"/>
-    <customWorkbookView name="Basil Odermatt - Persönliche Ansicht" guid="{59C26AB4-86C6-4447-8F9F-F1FCBFE3A683}" mergeInterval="0" personalView="1" maximized="1" xWindow="2552" yWindow="-6" windowWidth="2576" windowHeight="1426" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1229,12 +1229,6 @@
     <t>Electricity.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">CO₂-Emissionen kantonale Gebäude </t>
-  </si>
-  <si>
-    <t>CO₂-Emissionen kantonaler Gebäude (Mietermodell) pro m2 (witterungsbereinigt)</t>
-  </si>
-  <si>
     <t>Tonnen CO₂-Äquivalente (CO₂eq) pro Kopf</t>
   </si>
   <si>
@@ -1398,6 +1392,12 @@
   </si>
   <si>
     <t>sdmx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO₂-Emissionen Wärmeerzeugung kantonale Gebäude </t>
+  </si>
+  <si>
+    <t>CO₂-Emissionen Wärmeerzeugung kantonale Gebäude (Mietermodell) pro m2 (witterungsbereinigt)</t>
   </si>
 </sst>
 </file>
@@ -5347,7 +5347,7 @@
         <v>113</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>91</v>
@@ -5423,10 +5423,10 @@
         <v>181</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I6" s="31"/>
       <c r="J6" s="31" t="s">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="L6" s="31"/>
       <c r="M6" s="31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N6" s="25" t="s">
         <v>156</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="P6" s="25"/>
       <c r="Q6" s="25" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="R6" s="25"/>
       <c r="S6" s="25"/>
@@ -5456,7 +5456,7 @@
         <v>184</v>
       </c>
       <c r="V6" s="25" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W6" s="25" t="s">
         <v>185</v>
@@ -5625,13 +5625,13 @@
         <v>91</v>
       </c>
       <c r="F9" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>376</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>378</v>
       </c>
       <c r="J9" s="25" t="s">
         <v>86</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="W9" s="25"/>
       <c r="X9" s="25" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Y9" s="25" t="s">
         <v>159</v>
@@ -5678,13 +5678,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>91</v>
@@ -5696,7 +5696,7 @@
         <v>173</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J10" s="25" t="s">
         <v>86</v>
@@ -5716,19 +5716,19 @@
       </c>
       <c r="P10" s="25"/>
       <c r="Q10" s="31" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R10" s="25"/>
       <c r="S10" s="25"/>
       <c r="T10" s="25"/>
       <c r="U10" s="31" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="V10" s="25" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="W10" s="25" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="X10" s="25" t="s">
         <v>99</v>
@@ -5829,10 +5829,10 @@
         <v>181</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J12" s="25" t="s">
         <v>86</v>
@@ -5841,7 +5841,7 @@
         <v>2005</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N12" s="25" t="s">
         <v>156</v>
@@ -5859,7 +5859,7 @@
         <v>212</v>
       </c>
       <c r="V12" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W12" s="35" t="s">
         <v>213</v>
@@ -5919,7 +5919,7 @@
         <v>218</v>
       </c>
       <c r="U13" s="25" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="V13" s="25" t="s">
         <v>219</v>
@@ -5953,16 +5953,16 @@
         <v>221</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>181</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>86</v>
@@ -5974,7 +5974,7 @@
         <v>85</v>
       </c>
       <c r="U14" s="25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="V14" s="25" t="s">
         <v>222</v>
@@ -6000,7 +6000,7 @@
         <v>225</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>91</v>
@@ -6096,7 +6096,7 @@
         <v>237</v>
       </c>
       <c r="V16" s="25" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W16"/>
       <c r="X16" s="25" t="s">
@@ -6123,10 +6123,10 @@
         <v>81</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>347</v>
+        <v>402</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>348</v>
+        <v>403</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>91</v>
@@ -6153,7 +6153,7 @@
         <v>243</v>
       </c>
       <c r="V17" s="25" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W17"/>
       <c r="X17" s="25" t="s">
@@ -6249,7 +6249,7 @@
         <v>164</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J19" s="25" t="s">
         <v>86</v>
@@ -6292,10 +6292,10 @@
         <v>84</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>91</v>
@@ -6307,7 +6307,7 @@
         <v>164</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J20" s="25" t="s">
         <v>86</v>
@@ -6331,7 +6331,7 @@
         <v>93</v>
       </c>
       <c r="V20" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W20" s="35" t="s">
         <v>259</v>
@@ -6496,10 +6496,10 @@
         <v>181</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J23" s="25" t="s">
         <v>86</v>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="L23" s="25"/>
       <c r="M23" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N23" s="25" t="s">
         <v>156</v>
@@ -6530,7 +6530,7 @@
         <v>93</v>
       </c>
       <c r="V23" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W23" s="35" t="s">
         <v>276</v>
@@ -6568,10 +6568,10 @@
         <v>181</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I24" s="25"/>
       <c r="J24" s="25" t="s">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="L24" s="25"/>
       <c r="M24" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N24" s="25" t="s">
         <v>156</v>
@@ -6603,7 +6603,7 @@
         <v>93</v>
       </c>
       <c r="V24" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W24" s="35" t="s">
         <v>283</v>
@@ -6632,7 +6632,7 @@
         <v>58</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>285</v>
@@ -6644,10 +6644,10 @@
         <v>181</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I25" s="25"/>
       <c r="J25" s="25" t="s">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="L25" s="25"/>
       <c r="M25" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N25" s="25" t="s">
         <v>156</v>
@@ -6673,19 +6673,19 @@
         <v>287</v>
       </c>
       <c r="R25" s="25" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="S25" s="25" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="T25" s="25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>93</v>
       </c>
       <c r="V25" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W25" s="35" t="s">
         <v>288</v>
@@ -6726,10 +6726,10 @@
         <v>181</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I26" s="31"/>
       <c r="J26" s="31" t="s">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="L26" s="31"/>
       <c r="M26" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N26" s="25" t="s">
         <v>156</v>
@@ -6767,7 +6767,7 @@
         <v>93</v>
       </c>
       <c r="V26" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W26" s="35" t="s">
         <v>283</v>
@@ -6796,7 +6796,7 @@
         <v>60</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D27" s="25" t="s">
         <v>295</v>
@@ -6808,10 +6808,10 @@
         <v>181</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I27" s="25"/>
       <c r="J27" s="25" t="s">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="L27" s="25"/>
       <c r="M27" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N27" s="25" t="s">
         <v>156</v>
@@ -6840,16 +6840,16 @@
         <v>293</v>
       </c>
       <c r="S27" s="25" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="T27" s="25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>93</v>
       </c>
       <c r="V27" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W27" s="35" t="s">
         <v>283</v>
@@ -7177,7 +7177,7 @@
         <v>102</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I32" s="25"/>
       <c r="J32" s="25" t="s">
@@ -7196,25 +7196,25 @@
         <v>156</v>
       </c>
       <c r="O32" s="25" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P32" s="25">
         <v>16</v>
       </c>
       <c r="Q32" s="25" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="R32" s="25"/>
       <c r="S32" s="25"/>
       <c r="T32" s="25"/>
       <c r="U32" s="25" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="V32" s="25" t="s">
         <v>324</v>
       </c>
       <c r="X32" s="25" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Y32" s="25" t="s">
         <v>159</v>
@@ -7460,7 +7460,7 @@
         <v>105</v>
       </c>
       <c r="V36" s="25" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W36" s="25"/>
       <c r="X36" s="25" t="s">
@@ -7668,25 +7668,25 @@
         <v>1</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E40" s="25" t="s">
         <v>91</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G40" t="s">
         <v>173</v>
       </c>
       <c r="H40" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J40" t="s">
         <v>86</v>
@@ -7701,10 +7701,10 @@
         <v>93</v>
       </c>
       <c r="V40" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="X40" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Y40" t="s">
         <v>159</v>
@@ -7765,6 +7765,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c16c412-41a7-483e-8458-9b4c6e041c8c">
@@ -7773,15 +7782,6 @@
     <TaxCatchAll xmlns="9ff67bf8-4dc4-49ec-8a2f-3c58a02da8ea" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7990,6 +7990,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E4C368-1DF5-422B-BD39-8846CE2351EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18A314DA-0F62-4E10-94F7-DBFCC9F3B707}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -8002,14 +8010,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E4C368-1DF5-422B-BD39-8846CE2351EE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
